--- a/data/trans_bre/P1429-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1429-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>-0,07</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-16,15%</t>
+          <t>-7,5%</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 1,78</t>
+          <t>-3,6; 1,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,47</t>
+          <t>-1,08; 0,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 2,03</t>
+          <t>0,16; 2,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-19,74%</t>
+          <t>-21,78%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 1,28</t>
+          <t>-0,37; 1,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,13</t>
+          <t>-0,0; 1,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,46</t>
+          <t>-0,83; 0,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>1,25</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>379,27%</t>
+          <t>323,45%</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,99</t>
+          <t>1,02; 4,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,63</t>
+          <t>0,89; 3,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 1,97</t>
+          <t>-0,07; 1,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,96</t>
+          <t>0,43; 2,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,94; —</t>
+          <t>67,14; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-53,66; —</t>
+          <t>-64,99; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,21; 1977,45</t>
+          <t>20,06; 1623,19</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,52</t>
+          <t>5,61</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>543,63%</t>
+          <t>621,56%</t>
         </is>
       </c>
     </row>
@@ -1060,27 +1060,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 9,71</t>
+          <t>3,69; 9,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,46; 10,54</t>
+          <t>5,29; 10,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,66</t>
+          <t>2,25; 6,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,8; 7,22</t>
+          <t>3,95; 7,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>73,43; 883,61</t>
+          <t>86,41; 879,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>125,38; —</t>
+          <t>151,24; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>196,54; 1466,31</t>
+          <t>247,73; 1745,65</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>8,68</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>315,42%</t>
+          <t>555,9%</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,48; 13,29</t>
+          <t>5,1; 13,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,72; 12,19</t>
+          <t>5,94; 12,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,87; 15,38</t>
+          <t>8,31; 15,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,83; 9,37</t>
+          <t>6,36; 11,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>103,15; 870,33</t>
+          <t>101,07; 802,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>41,42; 810,49</t>
+          <t>238,82; 1278,51</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13,62</t>
+          <t>13,5</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>491,47%</t>
+          <t>465,56%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,98; 13,89</t>
+          <t>4,12; 13,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,59; 16,85</t>
+          <t>8,9; 16,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,9; 12,96</t>
+          <t>5,02; 13,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,86; 16,42</t>
+          <t>10,37; 16,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>52,0; 477,94</t>
+          <t>49,3; 478,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>118,64; —</t>
+          <t>127,57; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>106,78; 1132,62</t>
+          <t>104,84; 1014,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>262,74; 1010,25</t>
+          <t>208,93; 989,77</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,58</t>
+          <t>3,92</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>436,41%</t>
+          <t>467,76%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,06</t>
+          <t>2,51; 4,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,6</t>
+          <t>3,16; 4,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,47; 3,85</t>
+          <t>2,44; 3,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,31</t>
+          <t>3,29; 4,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>191,88; 533,47</t>
+          <t>190,19; 498,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>707,08; 6020,21</t>
+          <t>780,69; 5624,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>442,93; 1859,53</t>
+          <t>477,85; 1886,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>230,18; 733,67</t>
+          <t>261,49; 724,91</t>
         </is>
       </c>
     </row>
